--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_305_R31.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_305_R31.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>10.0557</v>
+        <v>10.4603</v>
       </c>
       <c r="E2" t="n">
-        <v>9.652799999999999</v>
+        <v>10.1246</v>
       </c>
       <c r="F2" t="n">
-        <v>0.4029</v>
+        <v>0.3357</v>
       </c>
       <c r="G2" t="n">
         <v>5.4515</v>
@@ -610,13 +610,13 @@
         <v>2.5515</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.1432</v>
+        <v>0.2614</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.4753</v>
+        <v>-0.0035</v>
       </c>
       <c r="U2" t="n">
-        <v>0.3321</v>
+        <v>0.2649</v>
       </c>
       <c r="V2" t="n">
         <v>2.428</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>J. HERNANGOMEZ</t>
+          <t>N. HAYES-DAVIS</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.2845</v>
+        <v>1.7288</v>
       </c>
       <c r="E3" t="n">
-        <v>2.6643</v>
+        <v>1.4964</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6202</v>
+        <v>0.2325</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.9395</v>
+        <v>0.2706</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.2603</v>
+        <v>-0.5726</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.6792</v>
+        <v>0.8431999999999999</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1292</v>
+        <v>1.3896</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.299</v>
+        <v>0.175</v>
       </c>
       <c r="L3" t="n">
-        <v>0.4282</v>
+        <v>1.2146</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.0687</v>
+        <v>-1.119</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0387</v>
+        <v>-0.7477</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.1074</v>
+        <v>-0.3713</v>
       </c>
       <c r="P3" t="n">
-        <v>0.9278</v>
+        <v>0.6959</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.232</v>
+        <v>-1.3917</v>
       </c>
       <c r="R3" t="n">
-        <v>1.1598</v>
+        <v>2.0876</v>
       </c>
       <c r="S3" t="n">
-        <v>2.7601</v>
+        <v>-0.168</v>
       </c>
       <c r="T3" t="n">
-        <v>1.6948</v>
+        <v>-0.1098</v>
       </c>
       <c r="U3" t="n">
-        <v>1.0653</v>
+        <v>-0.0582</v>
       </c>
       <c r="V3" t="n">
-        <v>0.5361</v>
+        <v>0.9304</v>
       </c>
       <c r="W3" t="n">
-        <v>1.0722</v>
+        <v>1.6083</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.5361</v>
+        <v>-0.6778999999999999</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>N. HAYES-DAVIS</t>
+          <t>J. HERNANGOMEZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.8297</v>
+        <v>1.5337</v>
       </c>
       <c r="E4" t="n">
-        <v>1.4964</v>
+        <v>1.4848</v>
       </c>
       <c r="F4" t="n">
-        <v>0.3333</v>
+        <v>0.0489</v>
       </c>
       <c r="G4" t="n">
-        <v>0.2706</v>
+        <v>-0.9395</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.5726</v>
+        <v>-0.2603</v>
       </c>
       <c r="I4" t="n">
-        <v>0.8431999999999999</v>
+        <v>-0.6792</v>
       </c>
       <c r="J4" t="n">
-        <v>1.3896</v>
+        <v>0.1292</v>
       </c>
       <c r="K4" t="n">
-        <v>0.175</v>
+        <v>-0.299</v>
       </c>
       <c r="L4" t="n">
-        <v>1.2146</v>
+        <v>0.4282</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.119</v>
+        <v>-1.0687</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.7477</v>
+        <v>0.0387</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.3713</v>
+        <v>-1.1074</v>
       </c>
       <c r="P4" t="n">
-        <v>0.6959</v>
+        <v>0.9278</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.3917</v>
+        <v>-0.232</v>
       </c>
       <c r="R4" t="n">
-        <v>2.0876</v>
+        <v>1.1598</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.0672</v>
+        <v>1.0093</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.1098</v>
+        <v>0.5153</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0426</v>
+        <v>0.494</v>
       </c>
       <c r="V4" t="n">
-        <v>0.9304</v>
+        <v>0.5361</v>
       </c>
       <c r="W4" t="n">
-        <v>1.6083</v>
+        <v>1.0722</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.6778999999999999</v>
+        <v>-0.5361</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>R. HOLMES</t>
+          <t>T. SHORTS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,40 +799,40 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.8415</v>
+        <v>1.1157</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.3942</v>
+        <v>0.951</v>
       </c>
       <c r="F5" t="n">
-        <v>1.2357</v>
+        <v>0.1647</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.0639</v>
+        <v>0.1106</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0431</v>
+        <v>1.0574</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.107</v>
+        <v>-0.9469</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.7324000000000001</v>
+        <v>0.2927</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.7324000000000001</v>
+        <v>0.2927</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>0.6685</v>
+        <v>-0.1821</v>
       </c>
       <c r="N5" t="n">
-        <v>0.7756</v>
+        <v>0.7648</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.107</v>
+        <v>-0.9469</v>
       </c>
       <c r="P5" t="n">
         <v>0.232</v>
@@ -844,19 +844,19 @@
         <v>0.232</v>
       </c>
       <c r="S5" t="n">
-        <v>0.6734</v>
+        <v>0.0953</v>
       </c>
       <c r="T5" t="n">
-        <v>0.3383</v>
+        <v>-0.0196</v>
       </c>
       <c r="U5" t="n">
-        <v>0.3352</v>
+        <v>0.1149</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>0.6778999999999999</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>0.6778999999999999</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>T. SHORTS</t>
+          <t>R. HOLMES</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,40 +877,40 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.5938</v>
+        <v>0.454</v>
       </c>
       <c r="E6" t="n">
-        <v>0.5971</v>
+        <v>-0.748</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.0033</v>
+        <v>1.2021</v>
       </c>
       <c r="G6" t="n">
-        <v>0.1106</v>
+        <v>-0.0639</v>
       </c>
       <c r="H6" t="n">
-        <v>1.0574</v>
+        <v>0.0431</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.9469</v>
+        <v>-0.107</v>
       </c>
       <c r="J6" t="n">
-        <v>0.2927</v>
+        <v>-0.7324000000000001</v>
       </c>
       <c r="K6" t="n">
-        <v>0.2927</v>
+        <v>-0.7324000000000001</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.1821</v>
+        <v>0.6685</v>
       </c>
       <c r="N6" t="n">
-        <v>0.7648</v>
+        <v>0.7756</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.9469</v>
+        <v>-0.107</v>
       </c>
       <c r="P6" t="n">
         <v>0.232</v>
@@ -922,19 +922,19 @@
         <v>0.232</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.4266</v>
+        <v>0.286</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.3734</v>
+        <v>-0.0156</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.0532</v>
+        <v>0.3016</v>
       </c>
       <c r="V6" t="n">
-        <v>0.6778999999999999</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>0.6778999999999999</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.5011</v>
+        <v>0.1552</v>
       </c>
       <c r="E7" t="n">
-        <v>0.2404</v>
+        <v>0.5942</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.7413999999999999</v>
+        <v>-0.439</v>
       </c>
       <c r="G7" t="n">
         <v>-0.221</v>
@@ -1000,13 +1000,13 @@
         <v>1.3917</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.4967</v>
+        <v>-0.8404</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.5895</v>
+        <v>-0.2357</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.9071</v>
+        <v>-0.6047</v>
       </c>
       <c r="V7" t="n">
         <v>2.1444</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.7531</v>
+        <v>-0.8875999999999999</v>
       </c>
       <c r="E8" t="n">
         <v>-1.0179</v>
       </c>
       <c r="F8" t="n">
-        <v>0.2647</v>
+        <v>0.1303</v>
       </c>
       <c r="G8" t="n">
         <v>-0.9622000000000001</v>
@@ -1078,13 +1078,13 @@
         <v>0.4639</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.2548</v>
+        <v>-0.3892</v>
       </c>
       <c r="T8" t="n">
         <v>-0.2987</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0439</v>
+        <v>-0.0905</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.9806</v>
+        <v>-1.9133</v>
       </c>
       <c r="E9" t="n">
         <v>-0.5604</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.4202</v>
+        <v>-1.353</v>
       </c>
       <c r="G9" t="n">
         <v>0.7376</v>
@@ -1156,13 +1156,13 @@
         <v>0.4639</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.8083</v>
+        <v>-0.7411</v>
       </c>
       <c r="T9" t="n">
         <v>-0.224</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.5843</v>
+        <v>-0.5171</v>
       </c>
       <c r="V9" t="n">
         <v>-1.214</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.3684</v>
+        <v>-2.3411</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.5738</v>
+        <v>-1.7481</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.7946</v>
+        <v>-0.593</v>
       </c>
       <c r="G11" t="n">
         <v>-2.6887</v>
@@ -1312,13 +1312,13 @@
         <v>2.5515</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.8626</v>
+        <v>-0.8353</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.187</v>
+        <v>-0.3613</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.6756</v>
+        <v>-0.474</v>
       </c>
       <c r="V11" t="n">
         <v>1.1829</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.5435</v>
+        <v>-3.8473</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.1946</v>
+        <v>-1.6664</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.3489</v>
+        <v>-2.1809</v>
       </c>
       <c r="G12" t="n">
         <v>-2.4526</v>
@@ -1390,13 +1390,13 @@
         <v>2.0876</v>
       </c>
       <c r="S12" t="n">
-        <v>0.6075</v>
+        <v>0.3038</v>
       </c>
       <c r="T12" t="n">
-        <v>0.9085</v>
+        <v>0.4367</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.3009</v>
+        <v>-0.1329</v>
       </c>
       <c r="V12" t="n">
         <v>-1.4665</v>
@@ -1423,31 +1423,31 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>4.3247</v>
+        <v>4.324599999999997</v>
       </c>
       <c r="E13" t="n">
-        <v>7.3335</v>
+        <v>7.3336</v>
       </c>
       <c r="F13" t="n">
-        <v>-3.0087</v>
+        <v>-3.0088</v>
       </c>
       <c r="G13" t="n">
         <v>-2.373199999999999</v>
       </c>
       <c r="H13" t="n">
-        <v>-1.303200000000001</v>
+        <v>-1.3032</v>
       </c>
       <c r="I13" t="n">
         <v>-1.0702</v>
       </c>
       <c r="J13" t="n">
-        <v>7.457400000000001</v>
+        <v>7.457400000000002</v>
       </c>
       <c r="K13" t="n">
-        <v>2.974299999999999</v>
+        <v>2.9743</v>
       </c>
       <c r="L13" t="n">
-        <v>4.4833</v>
+        <v>4.483300000000001</v>
       </c>
       <c r="M13" t="n">
         <v>-9.8309</v>
@@ -1468,13 +1468,13 @@
         <v>15.0771</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.7863999999999997</v>
+        <v>-0.7862000000000002</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.3512000000000003</v>
+        <v>-0.3513000000000001</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.4349000000000002</v>
+        <v>-0.4349000000000001</v>
       </c>
       <c r="V13" t="n">
         <v>4.0052</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>7.8553</v>
+        <v>8.484400000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>7.564</v>
+        <v>8.0359</v>
       </c>
       <c r="F14" t="n">
-        <v>0.2913</v>
+        <v>0.4485</v>
       </c>
       <c r="G14" t="n">
         <v>4.1235</v>
@@ -1546,13 +1546,13 @@
         <v>1.6237</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.0905</v>
+        <v>0.5386</v>
       </c>
       <c r="T14" t="n">
-        <v>0.0474</v>
+        <v>0.5192</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.1379</v>
+        <v>0.0193</v>
       </c>
       <c r="V14" t="n">
         <v>3.3584</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.9253</v>
+        <v>1.808</v>
       </c>
       <c r="E15" t="n">
-        <v>1.5581</v>
+        <v>1.6761</v>
       </c>
       <c r="F15" t="n">
-        <v>0.3672</v>
+        <v>0.1319</v>
       </c>
       <c r="G15" t="n">
         <v>1.1728</v>
@@ -1624,13 +1624,13 @@
         <v>0.4639</v>
       </c>
       <c r="S15" t="n">
-        <v>1.2191</v>
+        <v>1.1018</v>
       </c>
       <c r="T15" t="n">
-        <v>0.1968</v>
+        <v>0.3148</v>
       </c>
       <c r="U15" t="n">
-        <v>1.0223</v>
+        <v>0.787</v>
       </c>
       <c r="V15" t="n">
         <v>-0.9304</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>M. WRIGHT</t>
+          <t>D. GIEDRAITIS</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.5707</v>
+        <v>0.4043</v>
       </c>
       <c r="E16" t="n">
-        <v>1.8972</v>
+        <v>-0.0617</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.3266</v>
+        <v>0.466</v>
       </c>
       <c r="G16" t="n">
-        <v>1.8102</v>
+        <v>0.5036</v>
       </c>
       <c r="H16" t="n">
-        <v>1.4956</v>
+        <v>0.2727</v>
       </c>
       <c r="I16" t="n">
-        <v>0.3145</v>
+        <v>0.2309</v>
       </c>
       <c r="J16" t="n">
-        <v>3.1259</v>
+        <v>0.1072</v>
       </c>
       <c r="K16" t="n">
-        <v>2.3898</v>
+        <v>0.0336</v>
       </c>
       <c r="L16" t="n">
-        <v>0.7361</v>
+        <v>0.0736</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.3157</v>
+        <v>0.3963</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.8942</v>
+        <v>0.2391</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.4216</v>
+        <v>0.1573</v>
       </c>
       <c r="P16" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>-2.3195</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.1598</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>0.3145</v>
+        <v>-0.0993</v>
       </c>
       <c r="T16" t="n">
-        <v>0.4129</v>
+        <v>-0.1689</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.0984</v>
+        <v>0.0696</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.3943</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>0.6778999999999999</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. BUTKEVICIUS</t>
+          <t>M. WRIGHT</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0895</v>
+        <v>0.3347</v>
       </c>
       <c r="E17" t="n">
-        <v>0.3014</v>
+        <v>1.6613</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.2119</v>
+        <v>-1.3266</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.3496</v>
+        <v>1.8102</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.0552</v>
+        <v>1.4956</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.2944</v>
+        <v>0.3145</v>
       </c>
       <c r="J17" t="n">
-        <v>0.3761</v>
+        <v>3.1259</v>
       </c>
       <c r="K17" t="n">
-        <v>0.3025</v>
+        <v>2.3898</v>
       </c>
       <c r="L17" t="n">
-        <v>0.0736</v>
+        <v>0.7361</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.7257</v>
+        <v>-1.3157</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.3577</v>
+        <v>-0.8942</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.368</v>
+        <v>-0.4216</v>
       </c>
       <c r="P17" t="n">
-        <v>0.232</v>
+        <v>-1.1598</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-2.3195</v>
       </c>
       <c r="R17" t="n">
-        <v>0.232</v>
+        <v>1.1598</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.1871</v>
+        <v>0.0786</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.0747</v>
+        <v>0.177</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.1125</v>
+        <v>-0.0984</v>
       </c>
       <c r="V17" t="n">
-        <v>0.3943</v>
+        <v>-0.3943</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>0.6778999999999999</v>
       </c>
       <c r="X17" t="n">
-        <v>0.3943</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>D. GIEDRAITIS</t>
+          <t>A. BUTKEVICIUS</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.0504</v>
+        <v>0.1567</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.4155</v>
+        <v>0.3014</v>
       </c>
       <c r="F18" t="n">
-        <v>0.3652</v>
+        <v>-0.1447</v>
       </c>
       <c r="G18" t="n">
-        <v>0.5036</v>
+        <v>-0.3496</v>
       </c>
       <c r="H18" t="n">
-        <v>0.2727</v>
+        <v>-0.0552</v>
       </c>
       <c r="I18" t="n">
-        <v>0.2309</v>
+        <v>-0.2944</v>
       </c>
       <c r="J18" t="n">
-        <v>0.1072</v>
+        <v>0.3761</v>
       </c>
       <c r="K18" t="n">
-        <v>0.0336</v>
+        <v>0.3025</v>
       </c>
       <c r="L18" t="n">
         <v>0.0736</v>
       </c>
       <c r="M18" t="n">
-        <v>0.3963</v>
+        <v>-0.7257</v>
       </c>
       <c r="N18" t="n">
-        <v>0.2391</v>
+        <v>-0.3577</v>
       </c>
       <c r="O18" t="n">
-        <v>0.1573</v>
+        <v>-0.368</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>0.232</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>0.232</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.554</v>
+        <v>-0.1199</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.5228</v>
+        <v>-0.0747</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.0312</v>
+        <v>-0.0452</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>0.3943</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>0.3943</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.1159</v>
+        <v>-1.0151</v>
       </c>
       <c r="E19" t="n">
         <v>-1.0893</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.0265</v>
+        <v>0.0743</v>
       </c>
       <c r="G19" t="n">
         <v>-0.6445</v>
@@ -1936,13 +1936,13 @@
         <v>0.4639</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.9353</v>
+        <v>-0.8344</v>
       </c>
       <c r="T19" t="n">
         <v>-0.3734</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.5619</v>
+        <v>-0.461</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>D. SLEVA</t>
+          <t>E. ULANOVAS</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.1776</v>
+        <v>-1.3305</v>
       </c>
       <c r="E20" t="n">
-        <v>1.7446</v>
+        <v>-0.0977</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.9222</v>
+        <v>-1.2328</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.7472</v>
+        <v>0.3068</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.6038</v>
+        <v>-0.5029</v>
       </c>
       <c r="I20" t="n">
-        <v>0.8566</v>
+        <v>0.8097</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.6361</v>
+        <v>0.425</v>
       </c>
       <c r="K20" t="n">
-        <v>-1.6532</v>
+        <v>-0.7527</v>
       </c>
       <c r="L20" t="n">
-        <v>1.0171</v>
+        <v>1.1778</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.1111</v>
+        <v>-0.1182</v>
       </c>
       <c r="N20" t="n">
-        <v>0.0495</v>
+        <v>0.2499</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.1605</v>
+        <v>-0.368</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>0.4639</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.1598</v>
+        <v>0.4639</v>
       </c>
       <c r="S20" t="n">
-        <v>1.3196</v>
+        <v>-1.0291</v>
       </c>
       <c r="T20" t="n">
-        <v>1.3961</v>
+        <v>-0.5228</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.0764</v>
+        <v>-0.5063</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.7501</v>
+        <v>-1.0722</v>
       </c>
       <c r="W20" t="n">
-        <v>2.1444</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-3.8945</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>E. ULANOVAS</t>
+          <t>I. BRAZDEIKIS</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.4986</v>
+        <v>-1.3866</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.0977</v>
+        <v>-2.3548</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.4008</v>
+        <v>0.9681999999999999</v>
       </c>
       <c r="G21" t="n">
-        <v>0.3068</v>
+        <v>-2.5576</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.5029</v>
+        <v>-2.5341</v>
       </c>
       <c r="I21" t="n">
-        <v>0.8097</v>
+        <v>-0.0235</v>
       </c>
       <c r="J21" t="n">
-        <v>0.425</v>
+        <v>-2.4888</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.7527</v>
+        <v>-2.2043</v>
       </c>
       <c r="L21" t="n">
-        <v>1.1778</v>
+        <v>-0.2845</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.1182</v>
+        <v>-0.0687</v>
       </c>
       <c r="N21" t="n">
-        <v>0.2499</v>
+        <v>-0.3298</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.368</v>
+        <v>0.261</v>
       </c>
       <c r="P21" t="n">
-        <v>0.4639</v>
+        <v>1.1598</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>0.4639</v>
+        <v>1.1598</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.1971</v>
+        <v>0.6889999999999999</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.5228</v>
+        <v>0.134</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.6743</v>
+        <v>0.5551</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.0722</v>
+        <v>-0.6778999999999999</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.0722</v>
+        <v>-0.6778999999999999</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>I. BRAZDEIKIS</t>
+          <t>D. SLEVA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.9478</v>
+        <v>-1.6951</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.5907</v>
+        <v>0.801</v>
       </c>
       <c r="F22" t="n">
-        <v>0.6429</v>
+        <v>-2.4961</v>
       </c>
       <c r="G22" t="n">
-        <v>-2.5576</v>
+        <v>-0.7472</v>
       </c>
       <c r="H22" t="n">
-        <v>-2.5341</v>
+        <v>-1.6038</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.0235</v>
+        <v>0.8566</v>
       </c>
       <c r="J22" t="n">
-        <v>-2.4888</v>
+        <v>-0.6361</v>
       </c>
       <c r="K22" t="n">
-        <v>-2.2043</v>
+        <v>-1.6532</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.2845</v>
+        <v>1.0171</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.0687</v>
+        <v>-0.1111</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.3298</v>
+        <v>0.0495</v>
       </c>
       <c r="O22" t="n">
-        <v>0.261</v>
+        <v>-0.1605</v>
       </c>
       <c r="P22" t="n">
-        <v>1.1598</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R22" t="n">
         <v>1.1598</v>
       </c>
       <c r="S22" t="n">
-        <v>0.1278</v>
+        <v>0.8022</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.1019</v>
+        <v>0.4525</v>
       </c>
       <c r="U22" t="n">
-        <v>0.2298</v>
+        <v>0.3497</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.6778999999999999</v>
+        <v>-1.7501</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>2.1444</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.6778999999999999</v>
+        <v>-3.8945</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>N. WILLIAMS-GOSS</t>
+          <t>M. LO</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.5566</v>
+        <v>-2.1331</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.7305</v>
+        <v>-0.9842</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.8262</v>
+        <v>-1.149</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.0528</v>
+        <v>0.1929</v>
       </c>
       <c r="H23" t="n">
-        <v>1.7607</v>
+        <v>0.8957000000000001</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.8135</v>
+        <v>-0.7028</v>
       </c>
       <c r="J23" t="n">
-        <v>1.7811</v>
+        <v>2.3845</v>
       </c>
       <c r="K23" t="n">
-        <v>2.3835</v>
+        <v>2.0334</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.6022999999999999</v>
+        <v>0.3511</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.8339</v>
+        <v>-2.1916</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.6227</v>
+        <v>-1.1377</v>
       </c>
       <c r="O23" t="n">
-        <v>-1.2112</v>
+        <v>-1.0539</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.232</v>
+        <v>-2.0876</v>
       </c>
       <c r="Q23" t="n">
-        <v>-2.3195</v>
+        <v>-3.4793</v>
       </c>
       <c r="R23" t="n">
-        <v>2.0876</v>
+        <v>1.3917</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.2693</v>
+        <v>0.6919</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.3339</v>
+        <v>-0.0312</v>
       </c>
       <c r="U23" t="n">
-        <v>0.0646</v>
+        <v>0.7231</v>
       </c>
       <c r="V23" t="n">
-        <v>-2.0026</v>
+        <v>-0.9304</v>
       </c>
       <c r="W23" t="n">
         <v>0.1418</v>
       </c>
       <c r="X23" t="n">
-        <v>-2.1444</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>M. LO</t>
+          <t>N. WILLIAMS-GOSS</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.5948</v>
+        <v>-2.7247</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.6919</v>
+        <v>-0.7305</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.903</v>
+        <v>-1.9942</v>
       </c>
       <c r="G24" t="n">
-        <v>0.1929</v>
+        <v>-0.0528</v>
       </c>
       <c r="H24" t="n">
-        <v>0.8957000000000001</v>
+        <v>1.7607</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.7028</v>
+        <v>-1.8135</v>
       </c>
       <c r="J24" t="n">
-        <v>2.3845</v>
+        <v>1.7811</v>
       </c>
       <c r="K24" t="n">
-        <v>2.0334</v>
+        <v>2.3835</v>
       </c>
       <c r="L24" t="n">
-        <v>0.3511</v>
+        <v>-0.6022999999999999</v>
       </c>
       <c r="M24" t="n">
-        <v>-2.1916</v>
+        <v>-1.8339</v>
       </c>
       <c r="N24" t="n">
-        <v>-1.1377</v>
+        <v>-0.6227</v>
       </c>
       <c r="O24" t="n">
-        <v>-1.0539</v>
+        <v>-1.2112</v>
       </c>
       <c r="P24" t="n">
-        <v>-2.0876</v>
+        <v>-0.232</v>
       </c>
       <c r="Q24" t="n">
-        <v>-3.4793</v>
+        <v>-2.3195</v>
       </c>
       <c r="R24" t="n">
-        <v>1.3917</v>
+        <v>2.0876</v>
       </c>
       <c r="S24" t="n">
-        <v>0.2302</v>
+        <v>-0.4373</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.7389</v>
+        <v>-0.3339</v>
       </c>
       <c r="U24" t="n">
-        <v>0.9691</v>
+        <v>-0.1034</v>
       </c>
       <c r="V24" t="n">
-        <v>-0.9304</v>
+        <v>-2.0026</v>
       </c>
       <c r="W24" t="n">
         <v>0.1418</v>
       </c>
       <c r="X24" t="n">
-        <v>-1.0722</v>
+        <v>-2.1444</v>
       </c>
     </row>
     <row r="25">
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-3.8237</v>
+        <v>-4.4414</v>
       </c>
       <c r="E25" t="n">
-        <v>-3.4409</v>
+        <v>-4.1486</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.3829</v>
+        <v>-0.2928</v>
       </c>
       <c r="G25" t="n">
         <v>-1.3847</v>
@@ -2404,13 +2404,13 @@
         <v>1.3917</v>
       </c>
       <c r="S25" t="n">
-        <v>0.8083</v>
+        <v>0.1907</v>
       </c>
       <c r="T25" t="n">
-        <v>1.0499</v>
+        <v>0.3422</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.2416</v>
+        <v>-0.1516</v>
       </c>
       <c r="V25" t="n">
         <v>0</v>
@@ -2437,16 +2437,16 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-4.3246</v>
+        <v>-3.538399999999998</v>
       </c>
       <c r="E26" t="n">
-        <v>3.008799999999998</v>
+        <v>3.008900000000001</v>
       </c>
       <c r="F26" t="n">
-        <v>-7.3335</v>
+        <v>-6.5473</v>
       </c>
       <c r="G26" t="n">
-        <v>2.3734</v>
+        <v>2.373400000000002</v>
       </c>
       <c r="H26" t="n">
         <v>1.303</v>
@@ -2455,22 +2455,22 @@
         <v>1.0704</v>
       </c>
       <c r="J26" t="n">
-        <v>9.8307</v>
+        <v>9.830699999999998</v>
       </c>
       <c r="K26" t="n">
-        <v>4.277400000000001</v>
+        <v>4.2774</v>
       </c>
       <c r="L26" t="n">
-        <v>5.553500000000001</v>
+        <v>5.5535</v>
       </c>
       <c r="M26" t="n">
-        <v>-7.457400000000002</v>
+        <v>-7.4574</v>
       </c>
       <c r="N26" t="n">
         <v>-2.9741</v>
       </c>
       <c r="O26" t="n">
-        <v>-4.4831</v>
+        <v>-4.483099999999999</v>
       </c>
       <c r="P26" t="n">
         <v>-3.4793</v>
@@ -2482,13 +2482,13 @@
         <v>11.5978</v>
       </c>
       <c r="S26" t="n">
-        <v>0.7862</v>
+        <v>1.5728</v>
       </c>
       <c r="T26" t="n">
-        <v>0.4346999999999999</v>
+        <v>0.4348000000000001</v>
       </c>
       <c r="U26" t="n">
-        <v>0.3516</v>
+        <v>1.1379</v>
       </c>
       <c r="V26" t="n">
         <v>-4.0052</v>
